--- a/data/trans_camb/P20-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P20-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,29</t>
+          <t>-0,77; 3,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,99</t>
+          <t>-1,25; 2,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; -0,35</t>
+          <t>-3,53; -0,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 5,85</t>
+          <t>-1,55; 5,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 6,45</t>
+          <t>-1,04; 6,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 6,15</t>
+          <t>-3,1; 6,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,97</t>
+          <t>-0,27; 3,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,92</t>
+          <t>-0,31; 4,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 2,08</t>
+          <t>-2,77; 2,07</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 279,66</t>
+          <t>-34,7; 270,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-45,35; 256,52</t>
+          <t>-49,79; 235,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 94,16</t>
+          <t>-100,0; 66,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 146,24</t>
+          <t>-22,42; 114,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 146,56</t>
+          <t>-15,46; 131,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,77; 117,48</t>
+          <t>-45,24; 131,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 130,48</t>
+          <t>-5,79; 112,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 120,09</t>
+          <t>-6,71; 131,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-57,52; 68,13</t>
+          <t>-60,42; 69,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,43</t>
+          <t>-0,9; 3,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,1</t>
+          <t>-2,84; 0,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,74</t>
+          <t>-2,03; 3,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 6,38</t>
+          <t>-1,4; 6,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 2,96</t>
+          <t>-4,6; 2,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -1,05</t>
+          <t>-9,01; -0,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 4,22</t>
+          <t>-0,54; 4,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,47</t>
+          <t>-2,75; 1,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,71</t>
+          <t>-3,76; 0,84</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 147,69</t>
+          <t>-23,78; 143,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-65,76; 53,22</t>
+          <t>-69,92; 43,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,18; 156,16</t>
+          <t>-54,17; 173,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 64,83</t>
+          <t>-10,83; 62,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,97; 30,49</t>
+          <t>-34,49; 29,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,28; -8,53</t>
+          <t>-64,81; -7,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 67,02</t>
+          <t>-5,17; 66,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,25; 22,84</t>
+          <t>-33,7; 21,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,6; 11,66</t>
+          <t>-46,57; 12,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,16</t>
+          <t>0,58; 5,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,64</t>
+          <t>-1,36; 2,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,42</t>
+          <t>-1,04; 3,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,87</t>
+          <t>0,57; 5,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,84</t>
+          <t>0,23; 5,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,18</t>
+          <t>-0,75; 4,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,74</t>
+          <t>1,14; 4,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,28</t>
+          <t>0,05; 3,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,99</t>
+          <t>-0,26; 3,07</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,5; 260,19</t>
+          <t>11,51; 258,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 145,68</t>
+          <t>-38,08; 142,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 171,98</t>
+          <t>-30,89; 190,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,43; 151,6</t>
+          <t>5,13; 151,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 153,89</t>
+          <t>-0,91; 136,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 115,58</t>
+          <t>-13,8; 106,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,71; 148,54</t>
+          <t>22,62; 153,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 102,39</t>
+          <t>0,56; 106,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 95,96</t>
+          <t>-7,52; 92,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,66</t>
+          <t>-1,42; 3,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,4</t>
+          <t>-3,15; 1,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 2,76</t>
+          <t>-3,99; 2,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 6,3</t>
+          <t>0,34; 6,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,41</t>
+          <t>-2,69; 2,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,13</t>
+          <t>-3,46; 1,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,16</t>
+          <t>0,32; 4,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,21</t>
+          <t>-2,25; 1,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,22</t>
+          <t>-2,82; 1,27</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,82; 118,61</t>
+          <t>-26,72; 115,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,44; 54,65</t>
+          <t>-55,44; 48,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,11; 81,92</t>
+          <t>-63,4; 78,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 165,99</t>
+          <t>4,16; 178,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,18; 66,73</t>
+          <t>-42,19; 70,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,34; 29,74</t>
+          <t>-49,77; 35,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,06; 107,79</t>
+          <t>4,15; 114,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 33,83</t>
+          <t>-41,01; 32,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-46,96; 31,38</t>
+          <t>-48,82; 33,93</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,99</t>
+          <t>-1,55; 4,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 5,4</t>
+          <t>-0,8; 5,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 6,23</t>
+          <t>0,06; 6,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 3,98</t>
+          <t>-2,63; 4,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 1,99</t>
+          <t>-4,49; 2,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 1,88</t>
+          <t>-3,71; 1,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,55</t>
+          <t>-1,31; 3,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,95</t>
+          <t>-1,95; 2,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,35</t>
+          <t>-0,69; 3,33</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-23,36; 145,58</t>
+          <t>-23,73; 129,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 145,72</t>
+          <t>-16,25; 166,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0,61; 181,1</t>
+          <t>0,03; 178,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 86,2</t>
+          <t>-34,25; 95,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-52,71; 45,37</t>
+          <t>-55,11; 49,89</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-44,82; 45,15</t>
+          <t>-44,43; 42,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 83,37</t>
+          <t>-20,41; 79,78</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-26,22; 65,45</t>
+          <t>-27,76; 63,76</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 78,15</t>
+          <t>-11,55; 74,29</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 6,37</t>
+          <t>-2,95; 6,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 8,13</t>
+          <t>-1,41; 8,03</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 5,35</t>
+          <t>-2,53; 5,31</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 4,92</t>
+          <t>-3,09; 5,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 3,42</t>
+          <t>-4,98; 3,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,6; -1,68</t>
+          <t>-9,23; -1,53</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 4,38</t>
+          <t>-2,16; 4,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 4,0</t>
+          <t>-1,79; 4,12</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 0,6</t>
+          <t>-6,59; 0,39</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 110,28</t>
+          <t>-30,12; 107,93</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 144,19</t>
+          <t>-16,53; 141,29</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 104,3</t>
+          <t>-25,6; 91,34</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 75,53</t>
+          <t>-30,75; 82,11</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-46,77; 55,64</t>
+          <t>-47,46; 50,02</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-87,34; -24,56</t>
+          <t>-83,92; -20,64</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 59,15</t>
+          <t>-21,62; 65,1</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 56,72</t>
+          <t>-18,54; 59,55</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-65,51; 5,88</t>
+          <t>-65,15; 4,03</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 11,16</t>
+          <t>-0,52; 11,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 4,28</t>
+          <t>-5,92; 4,47</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 5,69</t>
+          <t>-3,14; 6,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 6,03</t>
+          <t>-3,43; 6,03</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 5,1</t>
+          <t>-4,24; 5,57</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 3,44</t>
+          <t>-4,43; 3,47</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 7,21</t>
+          <t>-0,98; 6,49</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 3,4</t>
+          <t>-3,73; 3,4</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 3,27</t>
+          <t>-2,64; 3,43</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 173,98</t>
+          <t>-7,6; 190,49</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-48,4; 64,72</t>
+          <t>-48,58; 71,88</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-30,71; 86,43</t>
+          <t>-26,45; 99,71</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 83,0</t>
+          <t>-27,68; 83,5</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-36,23; 68,86</t>
+          <t>-35,36; 78,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-35,48; 48,15</t>
+          <t>-33,87; 52,22</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 97,54</t>
+          <t>-8,74; 87,74</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-35,71; 43,48</t>
+          <t>-32,2; 44,87</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 44,44</t>
+          <t>-21,97; 45,31</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,08</t>
+          <t>0,87; 3,07</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,74</t>
+          <t>-0,37; 1,67</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,46</t>
+          <t>-0,13; 2,44</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,46</t>
+          <t>0,83; 3,51</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,71</t>
+          <t>-0,92; 1,56</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,18</t>
+          <t>-2,82; -0,21</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,92</t>
+          <t>1,08; 2,94</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,42</t>
+          <t>-0,34; 1,29</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,79</t>
+          <t>-1,12; 0,8</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>18,03; 85,72</t>
+          <t>19,09; 86,84</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 47,99</t>
+          <t>-8,53; 45,19</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2,06; 66,53</t>
+          <t>-2,29; 66,86</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9,42; 51,69</t>
+          <t>10,13; 52,15</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 25,69</t>
+          <t>-11,09; 23,3</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-35,19; -2,68</t>
+          <t>-36,1; -2,96</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,84; 54,66</t>
+          <t>17,48; 55,9</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 27,01</t>
+          <t>-5,43; 23,72</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 14,32</t>
+          <t>-18,15; 14,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P20-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P20-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-1,73</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-0,44</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,54</t>
+          <t>-0,91; 3,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,89</t>
+          <t>-1,01; 2,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,53; -0,32</t>
+          <t>-3,8; -0,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 5,47</t>
+          <t>-0,92; 5,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 6,09</t>
+          <t>-1,15; 6,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,09</t>
+          <t>-3,13; 6,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,56</t>
+          <t>-0,25; 3,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,02</t>
+          <t>-0,34; 3,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,07</t>
+          <t>-2,78; 2,15</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-82,29%</t>
+          <t>-84,46%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-17,48%</t>
+          <t>-11,09%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,7; 270,3</t>
+          <t>-36,87; 270,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,79; 235,15</t>
+          <t>-41,43; 283,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,64</t>
+          <t>-100,0; 40,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 114,66</t>
+          <t>-13,89; 129,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 131,5</t>
+          <t>-16,35; 135,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 131,4</t>
+          <t>-43,71; 136,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 112,16</t>
+          <t>-5,51; 114,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 131,09</t>
+          <t>-8,42; 121,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-60,42; 69,15</t>
+          <t>-59,64; 69,11</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,57</t>
+          <t>-3,3</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,56</t>
+          <t>-1,05</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,44</t>
+          <t>-0,8; 3,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,91</t>
+          <t>-2,78; 1,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 3,95</t>
+          <t>-2,03; 3,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 6,19</t>
+          <t>-1,68; 6,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 2,97</t>
+          <t>-5,12; 2,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,01; -0,72</t>
+          <t>-7,04; 0,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,03</t>
+          <t>-0,0; 4,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,28</t>
+          <t>-2,79; 1,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,84</t>
+          <t>-3,38; 1,23</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-38,45%</t>
+          <t>-27,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-21,73%</t>
+          <t>-14,59%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 143,38</t>
+          <t>-22,1; 140,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-69,92; 43,47</t>
+          <t>-66,26; 49,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,17; 173,89</t>
+          <t>-54,69; 163,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 62,77</t>
+          <t>-12,35; 64,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 29,74</t>
+          <t>-35,46; 27,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,81; -7,28</t>
+          <t>-50,52; 3,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 66,62</t>
+          <t>-1,38; 67,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,7; 21,07</t>
+          <t>-34,22; 20,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 12,36</t>
+          <t>-40,29; 21,19</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,06</t>
+          <t>0,41; 5,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,58</t>
+          <t>-1,22; 2,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,56</t>
+          <t>-1,11; 3,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,89</t>
+          <t>0,19; 5,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 5,43</t>
+          <t>0,11; 5,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,05</t>
+          <t>-0,7; 3,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,76</t>
+          <t>1,05; 4,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,4</t>
+          <t>0,06; 3,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,07</t>
+          <t>-0,26; 2,82</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,51; 258,79</t>
+          <t>4,36; 258,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,08; 142,34</t>
+          <t>-37,43; 140,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,89; 190,19</t>
+          <t>-32,37; 166,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,13; 151,53</t>
+          <t>2,01; 148,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 136,59</t>
+          <t>-1,14; 147,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 106,51</t>
+          <t>-11,92; 101,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,62; 153,58</t>
+          <t>22,45; 139,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 106,24</t>
+          <t>-0,2; 105,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 92,04</t>
+          <t>-6,08; 84,37</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-0,6</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>0,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,55</t>
+          <t>-1,38; 4,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,36</t>
+          <t>-3,16; 1,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 2,71</t>
+          <t>-0,87; 4,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 6,51</t>
+          <t>0,22; 6,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,58</t>
+          <t>-2,51; 2,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1,24</t>
+          <t>-3,13; 1,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,23</t>
+          <t>0,08; 4,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,21</t>
+          <t>-2,15; 1,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,27</t>
+          <t>-1,11; 2,31</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-1,92%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-18,4%</t>
+          <t>-12,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-10,61%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 115,75</t>
+          <t>-26,88; 144,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,44; 48,66</t>
+          <t>-55,43; 52,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 78,73</t>
+          <t>-18,08; 146,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,16; 178,46</t>
+          <t>-0,31; 159,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,19; 70,47</t>
+          <t>-42,69; 57,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,77; 35,73</t>
+          <t>-45,01; 43,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,15; 114,24</t>
+          <t>0,41; 111,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 32,0</t>
+          <t>-39,17; 40,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-48,82; 33,93</t>
+          <t>-19,96; 62,6</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>3,2</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,65</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 4,56</t>
+          <t>-1,73; 4,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,58</t>
+          <t>-0,79; 5,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 6,04</t>
+          <t>0,23; 6,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 4,23</t>
+          <t>-2,63; 4,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 2,18</t>
+          <t>-4,06; 2,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,8</t>
+          <t>-3,76; 1,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 3,46</t>
+          <t>-1,31; 3,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,77</t>
+          <t>-2,08; 2,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,33</t>
+          <t>-1,01; 3,23</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-12,7%</t>
+          <t>-10,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 129,49</t>
+          <t>-31,2; 123,98</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 166,32</t>
+          <t>-16,39; 155,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0,03; 178,68</t>
+          <t>1,69; 201,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,25; 95,33</t>
+          <t>-34,75; 91,8</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-55,11; 49,89</t>
+          <t>-53,49; 47,89</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 42,34</t>
+          <t>-43,85; 45,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-20,41; 79,78</t>
+          <t>-20,22; 69,58</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 63,76</t>
+          <t>-31,47; 53,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 74,29</t>
+          <t>-14,52; 72,54</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,9</t>
+          <t>-2,74</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-0,72</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 6,01</t>
+          <t>-3,06; 6,3</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 8,03</t>
+          <t>-2,0; 7,84</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 5,31</t>
+          <t>-2,31; 5,17</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 5,27</t>
+          <t>-3,22; 5,07</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 3,07</t>
+          <t>-5,13; 3,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,23; -1,53</t>
+          <t>-6,45; 0,14</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 4,36</t>
+          <t>-1,72; 4,63</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 4,12</t>
+          <t>-2,15; 4,27</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 0,39</t>
+          <t>-3,43; 1,83</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-57,17%</t>
+          <t>-31,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-28,31%</t>
+          <t>-8,8%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-30,12; 107,93</t>
+          <t>-33,48; 112,67</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 141,29</t>
+          <t>-20,59; 135,58</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 91,34</t>
+          <t>-23,8; 94,83</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,75; 82,11</t>
+          <t>-31,77; 77,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-47,46; 50,02</t>
+          <t>-48,78; 51,08</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-83,92; -20,64</t>
+          <t>-56,98; 3,59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 65,1</t>
+          <t>-17,95; 68,57</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 59,55</t>
+          <t>-21,88; 65,01</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-65,15; 4,03</t>
+          <t>-34,15; 28,64</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 11,79</t>
+          <t>-0,64; 11,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 4,47</t>
+          <t>-5,98; 3,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 6,12</t>
+          <t>-4,38; 5,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 6,03</t>
+          <t>-3,24; 6,62</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 5,57</t>
+          <t>-4,17; 5,5</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 3,47</t>
+          <t>-4,53; 3,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 6,49</t>
+          <t>-1,55; 6,68</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 3,4</t>
+          <t>-3,61; 3,44</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 3,43</t>
+          <t>-3,02; 3,08</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-2,32%</t>
+          <t>-3,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 190,49</t>
+          <t>-9,63; 186,32</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-48,58; 71,88</t>
+          <t>-49,41; 58,47</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-26,45; 99,71</t>
+          <t>-33,77; 87,42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-27,68; 83,5</t>
+          <t>-26,65; 98,66</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 78,85</t>
+          <t>-37,0; 74,86</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-33,87; 52,22</t>
+          <t>-36,23; 43,63</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 87,74</t>
+          <t>-13,91; 84,92</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 44,87</t>
+          <t>-31,69; 46,42</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-21,97; 45,31</t>
+          <t>-25,04; 40,25</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-0,81</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>0,42</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,07</t>
+          <t>0,84; 3,12</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,67</t>
+          <t>-0,33; 1,69</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,44</t>
+          <t>0,67; 2,76</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,51</t>
+          <t>0,87; 3,63</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,56</t>
+          <t>-0,91; 1,65</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,21</t>
+          <t>-2,1; 0,38</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,94</t>
+          <t>1,12; 2,94</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,29</t>
+          <t>-0,3; 1,39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,8</t>
+          <t>-0,33; 1,23</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-19,7%</t>
+          <t>-10,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-1,64%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>19,09; 86,84</t>
+          <t>17,44; 84,56</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 45,19</t>
+          <t>-7,04; 45,94</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 66,86</t>
+          <t>14,11; 77,03</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10,13; 52,15</t>
+          <t>11,11; 54,14</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 23,3</t>
+          <t>-11,37; 24,42</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-36,1; -2,96</t>
+          <t>-25,7; 5,75</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,48; 55,9</t>
+          <t>17,64; 53,73</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 23,72</t>
+          <t>-5,09; 25,84</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 14,83</t>
+          <t>-5,07; 23,79</t>
         </is>
       </c>
     </row>
